--- a/data/raw/GLNPO 2024 Spring/Erie/D20/Zoops/ER 91M D20 Spring 2024 24GE03I74 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Erie/D20/Zoops/ER 91M D20 Spring 2024 24GE03I74 Zoop.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ccm243\OneDrive - Cornell University\Desktop\GLNPO Counts\2024\Spring\Erie\d20\Zoops\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Erie\D20\Zoops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E866B6AD-F26D-4171-9E1C-22EB3089CA9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A8D78D5-DFE7-4BD7-BF67-E0A4D8CDBC1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{986F3F2E-8DC2-4FF0-A86C-E90BDB79537B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{986F3F2E-8DC2-4FF0-A86C-E90BDB79537B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$217</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1620" r:id="rId2"/>
+    <pivotCache cacheId="47" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -515,7 +515,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -533,7 +533,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4987,7 +4986,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{11E1DCE8-AC3F-4CBE-BAF9-DFF7CBD22883}" name="PivotTable1" cacheId="1620" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{11E1DCE8-AC3F-4CBE-BAF9-DFF7CBD22883}" name="PivotTable1" cacheId="47" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T5:X27" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -5457,20 +5456,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7879BDC9-3AF7-49AF-889E-297CFCD5F5CB}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:X217"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.90625" customWidth="1"/>
-    <col min="12" max="12" width="9.54296875" customWidth="1"/>
-    <col min="20" max="20" width="24.7265625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.81640625" customWidth="1"/>
-    <col min="23" max="23" width="4.1796875" customWidth="1"/>
-    <col min="24" max="24" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.88671875" customWidth="1"/>
+    <col min="12" max="12" width="9.5546875" customWidth="1"/>
+    <col min="20" max="20" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.77734375" customWidth="1"/>
+    <col min="23" max="23" width="4.21875" customWidth="1"/>
+    <col min="24" max="24" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5526,7 +5526,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -5579,7 +5579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -5632,7 +5632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -5685,7 +5685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -5744,7 +5744,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -5812,7 +5812,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -5867,18 +5867,17 @@
       <c r="T7" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="U7" s="11">
+      <c r="U7">
         <v>0</v>
       </c>
-      <c r="V7" s="11">
+      <c r="V7">
         <v>2</v>
       </c>
-      <c r="W7" s="11"/>
-      <c r="X7" s="11">
+      <c r="X7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -5933,18 +5932,17 @@
       <c r="T8" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="U8" s="11">
+      <c r="U8">
         <v>7</v>
       </c>
-      <c r="V8" s="11">
+      <c r="V8">
         <v>8</v>
       </c>
-      <c r="W8" s="11"/>
-      <c r="X8" s="11">
+      <c r="X8">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -5999,16 +5997,14 @@
       <c r="T9" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="U9" s="11">
+      <c r="U9">
         <v>35</v>
       </c>
-      <c r="V9" s="11"/>
-      <c r="W9" s="11"/>
-      <c r="X9" s="11">
+      <c r="X9">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -6063,18 +6059,17 @@
       <c r="T10" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="U10" s="11">
+      <c r="U10">
         <v>6</v>
       </c>
-      <c r="V10" s="11">
+      <c r="V10">
         <v>32</v>
       </c>
-      <c r="W10" s="11"/>
-      <c r="X10" s="11">
+      <c r="X10">
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -6129,16 +6124,14 @@
       <c r="T11" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="U11" s="11">
+      <c r="U11">
         <v>67</v>
       </c>
-      <c r="V11" s="11"/>
-      <c r="W11" s="11"/>
-      <c r="X11" s="11">
+      <c r="X11">
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -6193,16 +6186,14 @@
       <c r="T12" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="U12" s="11">
+      <c r="U12">
         <v>21</v>
       </c>
-      <c r="V12" s="11"/>
-      <c r="W12" s="11"/>
-      <c r="X12" s="11">
+      <c r="X12">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -6257,18 +6248,17 @@
       <c r="T13" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="U13" s="11">
+      <c r="U13">
         <v>2</v>
       </c>
-      <c r="V13" s="11">
+      <c r="V13">
         <v>3</v>
       </c>
-      <c r="W13" s="11"/>
-      <c r="X13" s="11">
+      <c r="X13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -6323,18 +6313,17 @@
       <c r="T14" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="U14" s="11">
+      <c r="U14">
         <v>3</v>
       </c>
-      <c r="V14" s="11">
+      <c r="V14">
         <v>6</v>
       </c>
-      <c r="W14" s="11"/>
-      <c r="X14" s="11">
+      <c r="X14">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -6389,18 +6378,17 @@
       <c r="T15" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="U15" s="11">
-        <v>1</v>
-      </c>
-      <c r="V15" s="11">
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
         <v>0</v>
       </c>
-      <c r="W15" s="11"/>
-      <c r="X15" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="X15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -6455,18 +6443,17 @@
       <c r="T16" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="U16" s="11">
+      <c r="U16">
         <v>0</v>
       </c>
-      <c r="V16" s="11">
-        <v>1</v>
-      </c>
-      <c r="W16" s="11"/>
-      <c r="X16" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="V16">
+        <v>1</v>
+      </c>
+      <c r="X16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -6521,16 +6508,14 @@
       <c r="T17" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="U17" s="11">
+      <c r="U17">
         <v>31</v>
       </c>
-      <c r="V17" s="11"/>
-      <c r="W17" s="11"/>
-      <c r="X17" s="11">
+      <c r="X17">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -6585,16 +6570,14 @@
       <c r="T18" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="U18" s="11">
+      <c r="U18">
         <v>67</v>
       </c>
-      <c r="V18" s="11"/>
-      <c r="W18" s="11"/>
-      <c r="X18" s="11">
+      <c r="X18">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -6649,18 +6632,17 @@
       <c r="T19" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="U19" s="11">
+      <c r="U19">
         <v>6</v>
       </c>
-      <c r="V19" s="11">
+      <c r="V19">
         <v>6</v>
       </c>
-      <c r="W19" s="11"/>
-      <c r="X19" s="11">
+      <c r="X19">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -6715,20 +6697,20 @@
       <c r="T20" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="U20" s="11">
+      <c r="U20">
         <v>0</v>
       </c>
-      <c r="V20" s="11">
+      <c r="V20">
         <v>0</v>
       </c>
-      <c r="W20" s="11">
-        <v>1</v>
-      </c>
-      <c r="X20" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -6783,18 +6765,17 @@
       <c r="T21" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="U21" s="11">
-        <v>1</v>
-      </c>
-      <c r="V21" s="11">
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21">
         <v>5</v>
       </c>
-      <c r="W21" s="11"/>
-      <c r="X21" s="11">
+      <c r="X21">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -6849,20 +6830,20 @@
       <c r="T22" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="U22" s="11">
+      <c r="U22">
         <v>0</v>
       </c>
-      <c r="V22" s="11">
+      <c r="V22">
         <v>3</v>
       </c>
-      <c r="W22" s="11">
+      <c r="W22">
         <v>3</v>
       </c>
-      <c r="X22" s="11">
+      <c r="X22">
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -6917,18 +6898,17 @@
       <c r="T23" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="U23" s="11">
+      <c r="U23">
         <v>5</v>
       </c>
-      <c r="V23" s="11">
+      <c r="V23">
         <v>8</v>
       </c>
-      <c r="W23" s="11"/>
-      <c r="X23" s="11">
+      <c r="X23">
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -6983,18 +6963,17 @@
       <c r="T24" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="U24" s="11">
+      <c r="U24">
         <v>0</v>
       </c>
-      <c r="V24" s="11">
-        <v>1</v>
-      </c>
-      <c r="W24" s="11"/>
-      <c r="X24" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="V24">
+        <v>1</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -7049,18 +7028,17 @@
       <c r="T25" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="U25" s="11">
+      <c r="U25">
         <v>0</v>
       </c>
-      <c r="V25" s="11">
+      <c r="V25">
         <v>2</v>
       </c>
-      <c r="W25" s="11"/>
-      <c r="X25" s="11">
+      <c r="X25">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -7115,18 +7093,17 @@
       <c r="T26" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="U26" s="11">
+      <c r="U26">
         <v>0</v>
       </c>
-      <c r="V26" s="11">
+      <c r="V26">
         <v>3</v>
       </c>
-      <c r="W26" s="11"/>
-      <c r="X26" s="11">
+      <c r="X26">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -7181,20 +7158,20 @@
       <c r="T27" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="U27" s="11">
+      <c r="U27">
         <v>252</v>
       </c>
-      <c r="V27" s="11">
+      <c r="V27">
         <v>80</v>
       </c>
-      <c r="W27" s="11">
+      <c r="W27">
         <v>4</v>
       </c>
-      <c r="X27" s="11">
+      <c r="X27">
         <v>336</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -7247,7 +7224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -7300,7 +7277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="16" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:24" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -7352,17 +7329,17 @@
       <c r="Q30">
         <v>1</v>
       </c>
-      <c r="T30" s="12" t="s">
+      <c r="T30" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="U30" s="13" t="s">
+      <c r="U30" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="V30" s="14">
+      <c r="V30" s="13">
         <v>1.0009999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="16" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:24" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -7414,15 +7391,15 @@
       <c r="Q31">
         <v>1</v>
       </c>
-      <c r="T31" s="15"/>
-      <c r="U31" s="13" t="s">
+      <c r="T31" s="14"/>
+      <c r="U31" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="V31" s="14">
+      <c r="V31" s="13">
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="16" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:24" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -7474,17 +7451,17 @@
       <c r="Q32">
         <v>1</v>
       </c>
-      <c r="T32" s="12" t="s">
+      <c r="T32" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="U32" s="13" t="s">
+      <c r="U32" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="V32" s="14">
+      <c r="V32" s="13">
         <v>1.0009999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:22" ht="16" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:22" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -7536,15 +7513,15 @@
       <c r="Q33">
         <v>1</v>
       </c>
-      <c r="T33" s="15"/>
-      <c r="U33" s="13" t="s">
+      <c r="T33" s="14"/>
+      <c r="U33" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="V33" s="14">
+      <c r="V33" s="13">
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:22" ht="16" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:22" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -7596,15 +7573,15 @@
       <c r="Q34">
         <v>1</v>
       </c>
-      <c r="T34" s="16" t="s">
+      <c r="T34" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="U34" s="17" t="s">
+      <c r="U34" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="V34" s="18"/>
-    </row>
-    <row r="35" spans="1:22" ht="16" x14ac:dyDescent="0.4">
+      <c r="V34" s="17"/>
+    </row>
+    <row r="35" spans="1:22" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -7656,15 +7633,15 @@
       <c r="Q35">
         <v>1</v>
       </c>
-      <c r="T35" s="16" t="s">
+      <c r="T35" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="U35" s="17" t="s">
+      <c r="U35" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="V35" s="18"/>
-    </row>
-    <row r="36" spans="1:22" ht="16" x14ac:dyDescent="0.4">
+      <c r="V35" s="17"/>
+    </row>
+    <row r="36" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -7716,13 +7693,13 @@
       <c r="Q36">
         <v>1</v>
       </c>
-      <c r="T36" s="13" t="s">
+      <c r="T36" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="U36" s="17"/>
-      <c r="V36" s="18"/>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="U36" s="16"/>
+      <c r="V36" s="17"/>
+    </row>
+    <row r="37" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -7775,7 +7752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -7828,7 +7805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -7881,7 +7858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -7934,7 +7911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -7987,7 +7964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -8040,7 +8017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -8093,7 +8070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -8146,7 +8123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -8199,7 +8176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -8252,7 +8229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -8305,7 +8282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -8358,7 +8335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -8411,7 +8388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -8464,7 +8441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -8517,7 +8494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -8570,7 +8547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -8623,7 +8600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -8676,7 +8653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -8729,7 +8706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -8782,7 +8759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -8835,7 +8812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -8888,7 +8865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -8941,7 +8918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -8994,7 +8971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -9047,7 +9024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -9100,7 +9077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -9153,7 +9130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -9206,7 +9183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -9259,7 +9236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -9312,7 +9289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -9365,7 +9342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -9418,7 +9395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -9471,7 +9448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -9524,7 +9501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -9577,7 +9554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -9630,7 +9607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -9683,7 +9660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -9736,7 +9713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -9789,7 +9766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -9842,7 +9819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -9895,7 +9872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -9948,7 +9925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -10001,7 +9978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -10054,7 +10031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -10107,7 +10084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -10163,7 +10140,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -10216,7 +10193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -10269,7 +10246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -10322,7 +10299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -10375,7 +10352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -10428,7 +10405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -10481,7 +10458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -10534,7 +10511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -10587,7 +10564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -10640,7 +10617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -10693,7 +10670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -10746,7 +10723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -10799,7 +10776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -10852,7 +10829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -10905,7 +10882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -10958,7 +10935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -11011,7 +10988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -11064,7 +11041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -11117,7 +11094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -11170,7 +11147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -11223,7 +11200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -11276,7 +11253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -11329,7 +11306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -11382,7 +11359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -11435,7 +11412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -11488,7 +11465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -11541,7 +11518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -11594,7 +11571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -11641,13 +11618,13 @@
         <v>0.875</v>
       </c>
       <c r="P110" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Q110">
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -11703,7 +11680,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -11756,7 +11733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -11809,7 +11786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -11862,7 +11839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -11915,7 +11892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -11968,7 +11945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -12021,7 +11998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -12074,7 +12051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -12127,7 +12104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -12180,7 +12157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -12233,7 +12210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -12289,7 +12266,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -12342,7 +12319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -12395,7 +12372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -12448,7 +12425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -12501,7 +12478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -12554,7 +12531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -12607,7 +12584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -12660,7 +12637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -12713,7 +12690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -12766,7 +12743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -12819,7 +12796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -12872,7 +12849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -12925,7 +12902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -12978,7 +12955,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -13031,7 +13008,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -13084,7 +13061,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -13137,7 +13114,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -13190,7 +13167,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -13243,7 +13220,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -13296,7 +13273,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -13349,7 +13326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -13402,7 +13379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -13455,7 +13432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -13508,7 +13485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -13561,7 +13538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -13614,7 +13591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -13667,7 +13644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -13720,7 +13697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -13773,7 +13750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -13826,7 +13803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -13879,7 +13856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -13932,7 +13909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -13985,7 +13962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -14038,7 +14015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -14091,7 +14068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>18</v>
       </c>
@@ -14144,7 +14121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -14197,7 +14174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -14250,7 +14227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -14303,7 +14280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>18</v>
       </c>
@@ -14356,7 +14333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -14409,7 +14386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -14462,7 +14439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>18</v>
       </c>
@@ -14515,7 +14492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -14568,7 +14545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -14621,7 +14598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>18</v>
       </c>
@@ -14674,7 +14651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>18</v>
       </c>
@@ -14727,7 +14704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>18</v>
       </c>
@@ -14780,7 +14757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>18</v>
       </c>
@@ -14833,7 +14810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -14886,7 +14863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -14939,7 +14916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -14992,7 +14969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>18</v>
       </c>
@@ -15045,7 +15022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>18</v>
       </c>
@@ -15098,7 +15075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -15151,7 +15128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -15204,7 +15181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -15257,7 +15234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>18</v>
       </c>
@@ -15310,7 +15287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -15363,7 +15340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>18</v>
       </c>
@@ -15416,7 +15393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -15472,7 +15449,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>18</v>
       </c>
@@ -15525,7 +15502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>18</v>
       </c>
@@ -15578,7 +15555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>18</v>
       </c>
@@ -15631,7 +15608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>18</v>
       </c>
@@ -15684,7 +15661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>18</v>
       </c>
@@ -15737,7 +15714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>18</v>
       </c>
@@ -15790,7 +15767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>18</v>
       </c>
@@ -15843,7 +15820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>18</v>
       </c>
@@ -15896,7 +15873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>18</v>
       </c>
@@ -15949,7 +15926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>18</v>
       </c>
@@ -16002,7 +15979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>18</v>
       </c>
@@ -16055,7 +16032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>18</v>
       </c>
@@ -16108,7 +16085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>18</v>
       </c>
@@ -16161,7 +16138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -16214,7 +16191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>18</v>
       </c>
@@ -16267,7 +16244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>18</v>
       </c>
@@ -16320,7 +16297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>18</v>
       </c>
@@ -16373,7 +16350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>18</v>
       </c>
@@ -16426,7 +16403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>18</v>
       </c>
@@ -16479,7 +16456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -16532,7 +16509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>18</v>
       </c>
@@ -16585,7 +16562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>18</v>
       </c>
@@ -16638,7 +16615,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>18</v>
       </c>
@@ -16691,7 +16668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>18</v>
       </c>
@@ -16744,7 +16721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>18</v>
       </c>
@@ -16797,7 +16774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>18</v>
       </c>
@@ -16850,7 +16827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="5" t="s">
         <v>18</v>
       </c>
@@ -16903,7 +16880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="5" t="s">
         <v>18</v>
       </c>
@@ -16956,7 +16933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="5" t="s">
         <v>18</v>
       </c>
@@ -17009,7 +16986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="5" t="s">
         <v>18</v>
       </c>
@@ -17062,7 +17039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="5" t="s">
         <v>18</v>
       </c>
@@ -17115,7 +17092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="5" t="s">
         <v>18</v>
       </c>
@@ -17168,7 +17145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="5" t="s">
         <v>18</v>
       </c>
@@ -17221,7 +17198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="5" t="s">
         <v>18</v>
       </c>
@@ -17274,7 +17251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="5" t="s">
         <v>18</v>
       </c>
@@ -17328,6 +17305,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R217" xr:uid="{7879BDC9-3AF7-49AF-889E-297CFCD5F5CB}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="Leptodiaptomus ashlandi"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>